--- a/outputs/20260825-community-research/Hobbeast_kozossegi_allitasok_emberi_felulvizsgalat_v1.12.0.xlsx
+++ b/outputs/20260825-community-research/Hobbeast_kozossegi_allitasok_emberi_felulvizsgalat_v1.12.0.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jegyzőkönyv" sheetId="1" r:id="R17a8ba66350344ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Felülvizsgálandó" sheetId="2" r:id="R2dc6c73aba444ba7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deduplikált" sheetId="3" r:id="R0eabbccc74f64a35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jegyzőkönyv" sheetId="1" r:id="Rf16be4cb44df4461"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Felülvizsgálandó" sheetId="2" r:id="Rd12ffc3f81c64c9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deduplikált" sheetId="3" r:id="R4b2e4d6178c04694"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13849,7 +13849,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Refd8c2d21cdf44b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc965d4aa5b444d7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16251,7 +16251,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb6d942a312e4b47"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2c42a94dbc74d61"/>
   </x:tableParts>
 </x:worksheet>
 </file>